--- a/Electronics_and_Communication_Engineering_Allotment.xlsx
+++ b/Electronics_and_Communication_Engineering_Allotment.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G18"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -551,19 +551,19 @@
         <v>4</v>
       </c>
       <c r="B7" t="str">
-        <v>Anwar Sherief</v>
+        <v>Bineesh B</v>
       </c>
       <c r="C7" t="str">
-        <v>1183</v>
+        <v>1650</v>
       </c>
       <c r="D7" t="str">
         <v>SM</v>
       </c>
       <c r="E7" t="str">
-        <v>anwarsherief08@gmail.com</v>
+        <v>bineeshbabu0003@gmail.com</v>
       </c>
       <c r="F7" t="str">
-        <v>7558837880</v>
+        <v>7559837724</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -574,19 +574,19 @@
         <v>5</v>
       </c>
       <c r="B8" t="str">
-        <v>Bineesh B</v>
+        <v>ABHIJITH BS</v>
       </c>
       <c r="C8" t="str">
-        <v>1650</v>
+        <v>1956</v>
       </c>
       <c r="D8" t="str">
         <v>SM</v>
       </c>
       <c r="E8" t="str">
-        <v>bineeshbabu0003@gmail.com</v>
+        <v>bsabhijith8@gmail.com</v>
       </c>
       <c r="F8" t="str">
-        <v>7559837724</v>
+        <v>6282072026</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -597,19 +597,19 @@
         <v>6</v>
       </c>
       <c r="B9" t="str">
-        <v>ADITHYAN S R</v>
+        <v>Adhithya Krishna S L</v>
       </c>
       <c r="C9" t="str">
-        <v>1724</v>
+        <v>3051</v>
       </c>
       <c r="D9" t="str">
         <v>SM</v>
       </c>
       <c r="E9" t="str">
-        <v>sr18adithyan@gmail.com</v>
+        <v>adhikrishna635@gmail.com</v>
       </c>
       <c r="F9" t="str">
-        <v>9633309755</v>
+        <v>9995334216</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -620,19 +620,19 @@
         <v>7</v>
       </c>
       <c r="B10" t="str">
-        <v>SHIJINA NIZAR</v>
+        <v>Nihal Noushad P</v>
       </c>
       <c r="C10" t="str">
-        <v>1894</v>
+        <v>796</v>
       </c>
       <c r="D10" t="str">
         <v>SM</v>
       </c>
       <c r="E10" t="str">
-        <v>shijinanizar14@gmail.com</v>
+        <v>nihalnazz0007@gmail.com</v>
       </c>
       <c r="F10" t="str">
-        <v>9747030732</v>
+        <v>8086657850</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -643,19 +643,19 @@
         <v>8</v>
       </c>
       <c r="B11" t="str">
-        <v>ABHIJITH BS</v>
+        <v>Anwar Sherief</v>
       </c>
       <c r="C11" t="str">
-        <v>1956</v>
+        <v>1183</v>
       </c>
       <c r="D11" t="str">
         <v>SM</v>
       </c>
       <c r="E11" t="str">
-        <v>bsabhijith8@gmail.com</v>
+        <v>anwarsherief08@gmail.com</v>
       </c>
       <c r="F11" t="str">
-        <v>6282072026</v>
+        <v>7558837880</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -666,19 +666,19 @@
         <v>9</v>
       </c>
       <c r="B12" t="str">
-        <v>RAIHANA RAHMAN</v>
+        <v>Muhammed Ashik S</v>
       </c>
       <c r="C12" t="str">
-        <v>2371</v>
+        <v>1536</v>
       </c>
       <c r="D12" t="str">
         <v>SM</v>
       </c>
       <c r="E12" t="str">
-        <v>raihanath.tech@gmail.com</v>
+        <v>ashikmohdd111@gmail.com</v>
       </c>
       <c r="F12" t="str">
-        <v>9778176204</v>
+        <v>9605619256</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -689,19 +689,19 @@
         <v>10</v>
       </c>
       <c r="B13" t="str">
-        <v>Jishnu saseendran</v>
+        <v>DEEPU V NAIR</v>
       </c>
       <c r="C13" t="str">
-        <v>2415</v>
+        <v>1545</v>
       </c>
       <c r="D13" t="str">
         <v>SM</v>
       </c>
       <c r="E13" t="str">
-        <v>jishnusaseendran82@gmail.com</v>
+        <v>deepuvnair2002@gmail.com</v>
       </c>
       <c r="F13" t="str">
-        <v>9633036381</v>
+        <v>7356682559</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -712,19 +712,19 @@
         <v>11</v>
       </c>
       <c r="B14" t="str">
-        <v>SUDHER BP</v>
+        <v>Sethumadhavan Sk</v>
       </c>
       <c r="C14" t="str">
-        <v>2434</v>
+        <v>2358</v>
       </c>
       <c r="D14" t="str">
         <v>SM</v>
       </c>
       <c r="E14" t="str">
-        <v>sudheerbp341@gmail.com</v>
+        <v>sksethumadhavan@gmail.com</v>
       </c>
       <c r="F14" t="str">
-        <v>8281885113</v>
+        <v>9496935402</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -735,19 +735,19 @@
         <v>12</v>
       </c>
       <c r="B15" t="str">
-        <v>Arif muhammad F</v>
+        <v>Kavya Sree B</v>
       </c>
       <c r="C15" t="str">
-        <v>2734</v>
+        <v>2893</v>
       </c>
       <c r="D15" t="str">
         <v>SM</v>
       </c>
       <c r="E15" t="str">
-        <v>arifbussid123@gmail.com</v>
+        <v>sreebkavya@gmail.com</v>
       </c>
       <c r="F15" t="str">
-        <v>8943145516</v>
+        <v>9400163906</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -758,19 +758,19 @@
         <v>13</v>
       </c>
       <c r="B16" t="str">
-        <v>Kavya Sree B</v>
+        <v>APARNA A</v>
       </c>
       <c r="C16" t="str">
-        <v>2893</v>
+        <v>3442</v>
       </c>
       <c r="D16" t="str">
         <v>SM</v>
       </c>
       <c r="E16" t="str">
-        <v>sreebkavya@gmail.com</v>
+        <v>aparanasamuvel@gmail.com</v>
       </c>
       <c r="F16" t="str">
-        <v>9400163906</v>
+        <v>8590895273</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -781,19 +781,19 @@
         <v>14</v>
       </c>
       <c r="B17" t="str">
-        <v>SHABANA SN</v>
+        <v>Ganesh A</v>
       </c>
       <c r="C17" t="str">
-        <v>2975</v>
+        <v>3601</v>
       </c>
       <c r="D17" t="str">
         <v>SM</v>
       </c>
       <c r="E17" t="str">
-        <v>akbarshabana1999@gmail.com</v>
+        <v>ganeshkumar10170@gmail.com</v>
       </c>
       <c r="F17" t="str">
-        <v>7034397207</v>
+        <v>6282562207</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -804,44 +804,21 @@
         <v>15</v>
       </c>
       <c r="B18" t="str">
-        <v>Rohan Raynish</v>
+        <v>Amal Krishna KR</v>
       </c>
       <c r="C18" t="str">
-        <v>2986</v>
+        <v>3680</v>
       </c>
       <c r="D18" t="str">
         <v>SM</v>
       </c>
       <c r="E18" t="str">
-        <v>rohanraynishh@gmail.com</v>
+        <v>amalkrkrishna6@gmail.com</v>
       </c>
       <c r="F18" t="str">
-        <v>7907345036</v>
+        <v>6235114058</v>
       </c>
       <c r="G18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>16</v>
-      </c>
-      <c r="B19" t="str">
-        <v>APARNA A</v>
-      </c>
-      <c r="C19" t="str">
-        <v>3442</v>
-      </c>
-      <c r="D19" t="str">
-        <v>SC</v>
-      </c>
-      <c r="E19" t="str">
-        <v>aparanasamuvel@gmail.com</v>
-      </c>
-      <c r="F19" t="str">
-        <v>8590895273</v>
-      </c>
-      <c r="G19" t="str">
         <v/>
       </c>
     </row>
@@ -851,7 +828,7 @@
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G18"/>
   </ignoredErrors>
 </worksheet>
 </file>